--- a/pipeline_output/NORTHEAST_2W_H&M.xlsx
+++ b/pipeline_output/NORTHEAST_2W_H&M.xlsx
@@ -681,7 +681,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, ASSAM, TRIPURA</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -736,12 +736,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, ASSAM, TRIPURA</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -853,12 +853,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, ASSAM, TRIPURA</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -980,12 +980,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, ASSAM, TRIPURA</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, ASSAM, TRIPURA</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, ASSAM, TRIPURA</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1361,12 +1361,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, ASSAM, TRIPURA</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, ASSAM, TRIPURA</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1732,12 +1732,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1849,12 +1849,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1976,12 +1976,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -2103,12 +2103,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -2546,7 +2546,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>ASSAM</t>
+          <t>ASSAM, NAGALAND</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>ASSAM</t>
+          <t>ASSAM, NAGALAND</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2845,12 +2845,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>ASSAM</t>
+          <t>ASSAM, NAGALAND</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>ASSAM</t>
+          <t>ASSAM, NAGALAND</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.5</t>
         </is>
       </c>
     </row>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>ASSAM</t>
+          <t>ASSAM, NAGALAND</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -3226,12 +3226,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>ASSAM</t>
+          <t>ASSAM, NAGALAND</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -3373,7 +3373,7 @@
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -3415,7 +3415,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>ASSAM</t>
+          <t>ASSAM, NAGALAND</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3480,12 +3480,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>ASSAM</t>
+          <t>ASSAM, NAGALAND</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, ASSAM, TRIPURA</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, ASSAM, TRIPURA</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3841,12 +3841,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, ASSAM, TRIPURA</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, ASSAM, TRIPURA</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -4095,12 +4095,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, ASSAM, TRIPURA</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -4222,12 +4222,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, ASSAM, TRIPURA</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -4349,12 +4349,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, ASSAM, TRIPURA</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, ASSAM, TRIPURA</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -4603,12 +4603,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -4720,12 +4720,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -4964,12 +4964,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
@@ -5407,7 +5407,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -5472,12 +5472,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -5599,12 +5599,12 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>ASSAM</t>
+          <t>ASSAM, NAGALAND</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>ASSAM</t>
+          <t>ASSAM, NAGALAND</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -5833,12 +5833,12 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
@@ -5895,7 +5895,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>ASSAM</t>
+          <t>ASSAM, NAGALAND</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -5960,12 +5960,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
@@ -6022,7 +6022,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>ASSAM</t>
+          <t>ASSAM, NAGALAND</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
@@ -6149,7 +6149,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>ASSAM</t>
+          <t>ASSAM, NAGALAND</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>ASSAM</t>
+          <t>ASSAM, NAGALAND</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
@@ -6403,7 +6403,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>ASSAM</t>
+          <t>ASSAM, NAGALAND</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -6468,12 +6468,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
@@ -6530,7 +6530,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>ASSAM</t>
+          <t>ASSAM, NAGALAND</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -6595,12 +6595,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
@@ -6657,7 +6657,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, ASSAM, TRIPURA</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -6712,12 +6712,12 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
@@ -6774,7 +6774,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, ASSAM, TRIPURA</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN51" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, ASSAM, TRIPURA</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN52" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
@@ -7008,7 +7008,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, ASSAM, TRIPURA</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -7063,12 +7063,12 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN53" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
@@ -7125,7 +7125,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, ASSAM, TRIPURA</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN54" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
@@ -7242,7 +7242,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, ASSAM, TRIPURA</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN55" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
@@ -7359,7 +7359,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, ASSAM, TRIPURA</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN56" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
@@ -7476,7 +7476,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, ASSAM, TRIPURA</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN57" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
@@ -7603,7 +7603,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, ASSAM, TRIPURA</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -7668,12 +7668,12 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN58" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
@@ -7730,7 +7730,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, ASSAM, TRIPURA</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -7785,12 +7785,12 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN59" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
@@ -7847,7 +7847,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, ASSAM, TRIPURA</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -7902,12 +7902,12 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN60" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
@@ -7964,7 +7964,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, ASSAM, TRIPURA</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -8019,12 +8019,12 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN61" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, ASSAM, TRIPURA</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -8136,12 +8136,12 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN62" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
@@ -8198,7 +8198,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN63" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -8380,12 +8380,12 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN64" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
@@ -8442,7 +8442,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -8507,12 +8507,12 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN65" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
@@ -8569,7 +8569,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -8624,12 +8624,12 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN66" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
@@ -8686,7 +8686,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -8751,12 +8751,12 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN67" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
@@ -8813,7 +8813,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN68" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
@@ -8940,7 +8940,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN69" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
@@ -9057,7 +9057,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -9112,12 +9112,12 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN70" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
@@ -9174,7 +9174,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN71" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
@@ -9291,7 +9291,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN72" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
@@ -9408,7 +9408,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN73" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
@@ -9525,7 +9525,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -9580,12 +9580,12 @@
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN74" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
@@ -9642,7 +9642,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN75" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
@@ -9769,7 +9769,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -9834,12 +9834,12 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN76" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
@@ -9896,7 +9896,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -9961,12 +9961,12 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN77" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
@@ -10023,7 +10023,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -10088,12 +10088,12 @@
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN78" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
@@ -10150,7 +10150,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -10205,12 +10205,12 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN79" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
@@ -10267,7 +10267,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -10322,12 +10322,12 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN80" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
@@ -10384,7 +10384,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -10439,12 +10439,12 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN81" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
@@ -10501,7 +10501,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN82" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -10693,12 +10693,12 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN83" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
@@ -10755,7 +10755,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN84" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
@@ -10872,7 +10872,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>ASSAM</t>
+          <t>ASSAM, NAGALAND</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN85" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
@@ -10989,7 +10989,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>ASSAM</t>
+          <t>ASSAM, NAGALAND</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN86" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
@@ -11106,7 +11106,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>ASSAM</t>
+          <t>ASSAM, NAGALAND</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -11161,12 +11161,12 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN87" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
@@ -11223,7 +11223,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>ASSAM</t>
+          <t>ASSAM, NAGALAND</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -11278,12 +11278,12 @@
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN88" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>ASSAM</t>
+          <t>ASSAM, NAGALAND</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -11395,12 +11395,12 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN89" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
@@ -11457,7 +11457,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>ASSAM</t>
+          <t>ASSAM, NAGALAND</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -11512,12 +11512,12 @@
       </c>
       <c r="AM90" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN90" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
@@ -11574,7 +11574,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>ASSAM</t>
+          <t>ASSAM, NAGALAND</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -11629,12 +11629,12 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN91" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
@@ -11691,7 +11691,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, ASSAM, TRIPURA</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="AM92" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN92" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
@@ -11808,7 +11808,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, ASSAM, TRIPURA</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -11873,12 +11873,12 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN93" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
@@ -11935,7 +11935,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, ASSAM, TRIPURA</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="AM94" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN94" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, ASSAM, TRIPURA</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN95" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
@@ -12189,7 +12189,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, ASSAM, TRIPURA</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN96" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
@@ -12316,7 +12316,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, ASSAM, TRIPURA</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -12371,12 +12371,12 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN97" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
@@ -12433,7 +12433,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, ASSAM, TRIPURA</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -12488,12 +12488,12 @@
       </c>
       <c r="AM98" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN98" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
@@ -12550,7 +12550,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, ASSAM, TRIPURA</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -12605,12 +12605,12 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN99" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
@@ -12667,7 +12667,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, ASSAM, TRIPURA</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -12722,12 +12722,12 @@
       </c>
       <c r="AM100" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN100" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
@@ -12784,7 +12784,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, ASSAM, TRIPURA</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -12839,12 +12839,12 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN101" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
@@ -12901,7 +12901,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, ASSAM, TRIPURA</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -12966,12 +12966,12 @@
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN102" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
@@ -13028,7 +13028,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, ASSAM, TRIPURA</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -13093,12 +13093,12 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN103" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
@@ -13155,7 +13155,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, ASSAM, TRIPURA</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -13220,12 +13220,12 @@
       </c>
       <c r="AM104" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN104" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
@@ -13282,7 +13282,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, ASSAM, TRIPURA</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -13347,12 +13347,12 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN105" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
@@ -13409,7 +13409,7 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, ASSAM, TRIPURA</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -13464,12 +13464,12 @@
       </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN106" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
@@ -13526,7 +13526,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, ASSAM, TRIPURA</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -13591,12 +13591,12 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN107" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
@@ -13653,7 +13653,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, ASSAM, TRIPURA</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -13718,12 +13718,12 @@
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN108" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO108" t="inlineStr">
@@ -13780,7 +13780,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, ASSAM, TRIPURA</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -13835,12 +13835,12 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN109" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
@@ -13897,7 +13897,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, ASSAM, TRIPURA</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN110" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO110" t="inlineStr">
@@ -14024,7 +14024,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, ASSAM, TRIPURA</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -14089,12 +14089,12 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN111" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO111" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, ASSAM, TRIPURA</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -14206,12 +14206,12 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN112" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
@@ -14268,7 +14268,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, ASSAM, TRIPURA</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -14333,12 +14333,12 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN113" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO113" t="inlineStr">
@@ -14395,7 +14395,7 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, ASSAM, TRIPURA</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -14460,12 +14460,12 @@
       </c>
       <c r="AM114" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN114" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO114" t="inlineStr">
@@ -14522,7 +14522,7 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -14577,12 +14577,12 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN115" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO115" t="inlineStr">
@@ -14639,7 +14639,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN116" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -14831,12 +14831,12 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN117" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
@@ -14893,7 +14893,7 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -14958,12 +14958,12 @@
       </c>
       <c r="AM118" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN118" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
@@ -15020,7 +15020,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -15085,12 +15085,12 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN119" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
@@ -15147,7 +15147,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -15202,12 +15202,12 @@
       </c>
       <c r="AM120" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN120" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
@@ -15264,7 +15264,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -15319,12 +15319,12 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN121" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
@@ -15381,7 +15381,7 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN122" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -15553,12 +15553,12 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN123" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO123" t="inlineStr">
@@ -15615,7 +15615,7 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -15670,12 +15670,12 @@
       </c>
       <c r="AM124" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN124" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO124" t="inlineStr">
@@ -15732,7 +15732,7 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -15797,12 +15797,12 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN125" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
@@ -15859,7 +15859,7 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -15924,12 +15924,12 @@
       </c>
       <c r="AM126" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN126" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO126" t="inlineStr">
@@ -15986,7 +15986,7 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -16051,12 +16051,12 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN127" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
@@ -16113,7 +16113,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -16178,12 +16178,12 @@
       </c>
       <c r="AM128" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN128" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO128" t="inlineStr">
@@ -16240,7 +16240,7 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -16295,12 +16295,12 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN129" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO129" t="inlineStr">
@@ -16357,7 +16357,7 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -16422,12 +16422,12 @@
       </c>
       <c r="AM130" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN130" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO130" t="inlineStr">
@@ -16484,7 +16484,7 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -16549,12 +16549,12 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN131" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO131" t="inlineStr">
@@ -16611,7 +16611,7 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -16666,12 +16666,12 @@
       </c>
       <c r="AM132" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN132" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO132" t="inlineStr">
@@ -16728,7 +16728,7 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -16793,12 +16793,12 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN133" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO133" t="inlineStr">
@@ -16855,7 +16855,7 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -16920,12 +16920,12 @@
       </c>
       <c r="AM134" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN134" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO134" t="inlineStr">
@@ -16982,7 +16982,7 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -17037,12 +17037,12 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN135" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO135" t="inlineStr">
@@ -17099,7 +17099,7 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -17164,12 +17164,12 @@
       </c>
       <c r="AM136" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN136" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO136" t="inlineStr">
@@ -17226,7 +17226,7 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, ODISHA, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -17291,12 +17291,12 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN137" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO137" t="inlineStr">
@@ -17353,7 +17353,7 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>ASSAM</t>
+          <t>ASSAM, NAGALAND</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -17408,12 +17408,12 @@
       </c>
       <c r="AM138" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN138" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO138" t="inlineStr">
@@ -17470,7 +17470,7 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>ASSAM</t>
+          <t>ASSAM, NAGALAND</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -17535,12 +17535,12 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN139" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO139" t="inlineStr">
@@ -17597,7 +17597,7 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>ASSAM</t>
+          <t>ASSAM, NAGALAND</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -17662,12 +17662,12 @@
       </c>
       <c r="AM140" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN140" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO140" t="inlineStr">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>ASSAM</t>
+          <t>ASSAM, NAGALAND</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -17789,12 +17789,12 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN141" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO141" t="inlineStr">
@@ -17851,7 +17851,7 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>ASSAM</t>
+          <t>ASSAM, NAGALAND</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -17916,12 +17916,12 @@
       </c>
       <c r="AM142" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN142" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO142" t="inlineStr">
@@ -17978,7 +17978,7 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>ASSAM</t>
+          <t>ASSAM, NAGALAND</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -18033,12 +18033,12 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN143" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO143" t="inlineStr">
@@ -18095,7 +18095,7 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>ASSAM</t>
+          <t>ASSAM, NAGALAND</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -18150,12 +18150,12 @@
       </c>
       <c r="AM144" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN144" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO144" t="inlineStr">
@@ -18212,7 +18212,7 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>ASSAM</t>
+          <t>ASSAM, NAGALAND</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -18267,12 +18267,12 @@
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN145" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO145" t="inlineStr">
@@ -18329,7 +18329,7 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>ASSAM</t>
+          <t>ASSAM, NAGALAND</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -18384,12 +18384,12 @@
       </c>
       <c r="AM146" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN146" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO146" t="inlineStr">
@@ -18446,7 +18446,7 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>ASSAM</t>
+          <t>ASSAM, NAGALAND</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -18501,12 +18501,12 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN147" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO147" t="inlineStr">
@@ -18563,7 +18563,7 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>ASSAM</t>
+          <t>ASSAM, NAGALAND</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -18628,12 +18628,12 @@
       </c>
       <c r="AM148" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN148" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO148" t="inlineStr">
@@ -18690,7 +18690,7 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>ASSAM</t>
+          <t>ASSAM, NAGALAND</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -18755,12 +18755,12 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN149" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO149" t="inlineStr">
@@ -18817,7 +18817,7 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>ASSAM</t>
+          <t>ASSAM, NAGALAND</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -18882,12 +18882,12 @@
       </c>
       <c r="AM150" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN150" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO150" t="inlineStr">
@@ -18944,7 +18944,7 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>ASSAM</t>
+          <t>ASSAM, NAGALAND</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -19009,12 +19009,12 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN151" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO151" t="inlineStr">
@@ -19071,7 +19071,7 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>ASSAM</t>
+          <t>ASSAM, NAGALAND</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -19126,12 +19126,12 @@
       </c>
       <c r="AM152" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN152" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
@@ -19188,7 +19188,7 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>ASSAM</t>
+          <t>ASSAM, NAGALAND</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -19253,12 +19253,12 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN153" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO153" t="inlineStr">
@@ -19315,7 +19315,7 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>ASSAM</t>
+          <t>ASSAM, NAGALAND</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -19380,12 +19380,12 @@
       </c>
       <c r="AM154" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN154" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO154" t="inlineStr">
@@ -19442,7 +19442,7 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>ASSAM</t>
+          <t>ASSAM, NAGALAND</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -19497,12 +19497,12 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN155" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO155" t="inlineStr">
@@ -19559,7 +19559,7 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>ASSAM</t>
+          <t>ASSAM, NAGALAND</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -19624,12 +19624,12 @@
       </c>
       <c r="AM156" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN156" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO156" t="inlineStr">
@@ -19686,7 +19686,7 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>ASSAM</t>
+          <t>ASSAM, NAGALAND</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -19751,12 +19751,12 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN157" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO157" t="inlineStr">
@@ -19813,7 +19813,7 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>ASSAM</t>
+          <t>ASSAM, NAGALAND</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -19868,12 +19868,12 @@
       </c>
       <c r="AM158" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN158" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO158" t="inlineStr">
@@ -19930,7 +19930,7 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>ASSAM</t>
+          <t>ASSAM, NAGALAND</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -19995,12 +19995,12 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN159" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO159" t="inlineStr">
@@ -20057,7 +20057,7 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>ASSAM</t>
+          <t>ASSAM, NAGALAND</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -20122,12 +20122,12 @@
       </c>
       <c r="AM160" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN160" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO160" t="inlineStr">
@@ -20249,12 +20249,12 @@
       </c>
       <c r="AM161" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN161" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO161" t="inlineStr">
@@ -20376,12 +20376,12 @@
       </c>
       <c r="AM162" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN162" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO162" t="inlineStr">
@@ -20503,12 +20503,12 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN163" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO163" t="inlineStr">
@@ -20630,12 +20630,12 @@
       </c>
       <c r="AM164" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN164" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO164" t="inlineStr">
@@ -20757,12 +20757,12 @@
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN165" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO165" t="inlineStr">
@@ -20884,12 +20884,12 @@
       </c>
       <c r="AM166" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN166" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO166" t="inlineStr">
@@ -21011,12 +21011,12 @@
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN167" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO167" t="inlineStr">
@@ -21138,12 +21138,12 @@
       </c>
       <c r="AM168" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN168" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO168" t="inlineStr">
@@ -21255,12 +21255,12 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN169" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO169" t="inlineStr">
@@ -21372,12 +21372,12 @@
       </c>
       <c r="AM170" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN170" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO170" t="inlineStr">
@@ -21489,12 +21489,12 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN171" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO171" t="inlineStr">
@@ -21606,12 +21606,12 @@
       </c>
       <c r="AM172" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN172" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO172" t="inlineStr">
@@ -21723,12 +21723,12 @@
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN173" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO173" t="inlineStr">
@@ -21840,12 +21840,12 @@
       </c>
       <c r="AM174" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN174" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO174" t="inlineStr">
@@ -21957,12 +21957,12 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN175" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO175" t="inlineStr">
@@ -22074,12 +22074,12 @@
       </c>
       <c r="AM176" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN176" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO176" t="inlineStr">
@@ -22191,12 +22191,12 @@
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN177" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO177" t="inlineStr">
@@ -22308,12 +22308,12 @@
       </c>
       <c r="AM178" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN178" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO178" t="inlineStr">
@@ -22425,12 +22425,12 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN179" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO179" t="inlineStr">
@@ -22542,12 +22542,12 @@
       </c>
       <c r="AM180" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN180" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO180" t="inlineStr">
@@ -22659,12 +22659,12 @@
       </c>
       <c r="AM181" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN181" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO181" t="inlineStr">
@@ -22776,12 +22776,12 @@
       </c>
       <c r="AM182" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN182" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO182" t="inlineStr">
@@ -22893,12 +22893,12 @@
       </c>
       <c r="AM183" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN183" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO183" t="inlineStr">
@@ -23010,12 +23010,12 @@
       </c>
       <c r="AM184" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN184" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO184" t="inlineStr">
@@ -23072,7 +23072,7 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, NAGALAND, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
@@ -23137,12 +23137,12 @@
       </c>
       <c r="AM185" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN185" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO185" t="inlineStr">
@@ -23199,7 +23199,7 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, NAGALAND, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -23264,12 +23264,12 @@
       </c>
       <c r="AM186" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN186" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO186" t="inlineStr">
@@ -23326,7 +23326,7 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, NAGALAND, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -23391,12 +23391,12 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN187" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO187" t="inlineStr">
@@ -23453,7 +23453,7 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, NAGALAND, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
@@ -23518,12 +23518,12 @@
       </c>
       <c r="AM188" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN188" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO188" t="inlineStr">
@@ -23580,7 +23580,7 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, NAGALAND, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -23645,12 +23645,12 @@
       </c>
       <c r="AM189" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN189" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO189" t="inlineStr">
@@ -23707,7 +23707,7 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, NAGALAND, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
@@ -23772,12 +23772,12 @@
       </c>
       <c r="AM190" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN190" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO190" t="inlineStr">
@@ -23834,7 +23834,7 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, NAGALAND, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
@@ -23899,12 +23899,12 @@
       </c>
       <c r="AM191" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN191" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO191" t="inlineStr">
@@ -23961,7 +23961,7 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, NAGALAND, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
@@ -24026,12 +24026,12 @@
       </c>
       <c r="AM192" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN192" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO192" t="inlineStr">
@@ -24088,7 +24088,7 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, NAGALAND, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -24143,12 +24143,12 @@
       </c>
       <c r="AM193" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN193" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO193" t="inlineStr">
@@ -24205,7 +24205,7 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, NAGALAND, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -24260,12 +24260,12 @@
       </c>
       <c r="AM194" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN194" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO194" t="inlineStr">
@@ -24322,7 +24322,7 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, NAGALAND, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -24377,12 +24377,12 @@
       </c>
       <c r="AM195" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN195" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO195" t="inlineStr">
@@ -24439,7 +24439,7 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, NAGALAND, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
@@ -24494,12 +24494,12 @@
       </c>
       <c r="AM196" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN196" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO196" t="inlineStr">
@@ -24556,7 +24556,7 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, NAGALAND, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -24611,12 +24611,12 @@
       </c>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN197" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO197" t="inlineStr">
@@ -24673,7 +24673,7 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, NAGALAND, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -24728,12 +24728,12 @@
       </c>
       <c r="AM198" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN198" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO198" t="inlineStr">
@@ -24790,7 +24790,7 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, NAGALAND, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -24845,12 +24845,12 @@
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN199" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO199" t="inlineStr">
@@ -24907,7 +24907,7 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, NAGALAND, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -24962,12 +24962,12 @@
       </c>
       <c r="AM200" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN200" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO200" t="inlineStr">
@@ -25024,7 +25024,7 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, NAGALAND, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
@@ -25079,12 +25079,12 @@
       </c>
       <c r="AM201" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN201" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO201" t="inlineStr">
@@ -25141,7 +25141,7 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, NAGALAND, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -25196,12 +25196,12 @@
       </c>
       <c r="AM202" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN202" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO202" t="inlineStr">
@@ -25258,7 +25258,7 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, NAGALAND, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
@@ -25313,12 +25313,12 @@
       </c>
       <c r="AM203" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN203" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO203" t="inlineStr">
@@ -25375,7 +25375,7 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, NAGALAND, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
@@ -25430,12 +25430,12 @@
       </c>
       <c r="AM204" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN204" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO204" t="inlineStr">
@@ -25492,7 +25492,7 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, NAGALAND, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
@@ -25547,12 +25547,12 @@
       </c>
       <c r="AM205" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN205" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO205" t="inlineStr">
@@ -25609,7 +25609,7 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, NAGALAND, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
@@ -25664,12 +25664,12 @@
       </c>
       <c r="AM206" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN206" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO206" t="inlineStr">
@@ -25726,7 +25726,7 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, NAGALAND, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
@@ -25781,12 +25781,12 @@
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN207" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO207" t="inlineStr">
@@ -25843,7 +25843,7 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>ARUNACHAL PRADESH</t>
+          <t>ARUNACHAL PRADESH, MEGHALAYA, MANIPUR, MIZORAM, NAGALAND, SIKKIM, TRIPURA</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
@@ -25898,12 +25898,12 @@
       </c>
       <c r="AM208" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN208" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO208" t="inlineStr">
